--- a/artfynd/Käringberget SV artfynd.xlsx
+++ b/artfynd/Käringberget SV artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103618172</v>
+        <v>84766650</v>
       </c>
       <c r="B2" t="n">
-        <v>78738</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+          <t>Yttersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677055</v>
+        <v>675874</v>
       </c>
       <c r="R2" t="n">
-        <v>7111386</v>
+        <v>7111403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,66 +756,61 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Carl Jansson</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103618191</v>
+        <v>84766648</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
+        <v>79864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>298</v>
+        <v>1352</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+          <t>Yttersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676991</v>
+        <v>676012</v>
       </c>
       <c r="R3" t="n">
-        <v>7111031</v>
+        <v>7111071</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,66 +853,61 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Carl Jansson</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103618174</v>
+        <v>84766646</v>
       </c>
       <c r="B4" t="n">
-        <v>90283</v>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+          <t>Yttersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>677004</v>
+        <v>676015</v>
       </c>
       <c r="R4" t="n">
-        <v>7111334</v>
+        <v>7111072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -960,31 +950,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Carl Jansson</t>
+          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103618182</v>
+        <v>107162697</v>
       </c>
       <c r="B5" t="n">
-        <v>80119</v>
+        <v>56766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100077</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+          <t>Storaggan (AC601), Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676935</v>
+        <v>676364</v>
       </c>
       <c r="R5" t="n">
-        <v>7111134</v>
+        <v>7111147</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,14 +1029,19 @@
           <t>Fredrika</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>AC601</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2016-09-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2016-09-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1062,31 +1052,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Darius Strasevicius</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Darius Strasevicius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Utter barmarksinventering RMÖ/GDP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796272</v>
+        <v>1990837</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,41 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fredrika, Ås lm</t>
+          <t>11 km ONO om Fredrika, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676855</v>
+        <v>676461</v>
       </c>
       <c r="R6" t="n">
-        <v>7111501</v>
+        <v>7111499</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1152,17 +1137,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2005-07-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2005-07-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,57 +1157,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84766648</v>
+        <v>103618191</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>92332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1352</v>
+        <v>298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yttersjön, Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676012</v>
+        <v>676991</v>
       </c>
       <c r="R7" t="n">
-        <v>7111071</v>
+        <v>7111031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1254,12 +1234,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,26 +1250,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103618195</v>
+        <v>103618201</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1321,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676992</v>
+        <v>677035</v>
       </c>
       <c r="R8" t="n">
-        <v>7110988</v>
+        <v>7110865</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,6 +1352,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1383,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103618161</v>
+        <v>103618198</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1418,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677129</v>
+        <v>677013</v>
       </c>
       <c r="R9" t="n">
-        <v>7111504</v>
+        <v>7110889</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,7 +1457,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1485,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103618157</v>
+        <v>103618203</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677176</v>
+        <v>677034</v>
       </c>
       <c r="R10" t="n">
-        <v>7111509</v>
+        <v>7110861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103618165</v>
+        <v>103618197</v>
       </c>
       <c r="B11" t="n">
-        <v>91263</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,21 +1583,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1617,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677095</v>
+        <v>676997</v>
       </c>
       <c r="R11" t="n">
-        <v>7111476</v>
+        <v>7110951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,11 +1653,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>granstubbe</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1684,32 +1669,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103618196</v>
+        <v>103618193</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676996</v>
+        <v>676979</v>
       </c>
       <c r="R12" t="n">
-        <v>7110957</v>
+        <v>7111017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,6 +1750,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1781,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103618179</v>
+        <v>103618200</v>
       </c>
       <c r="B13" t="n">
-        <v>91263</v>
+        <v>90691</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676934</v>
+        <v>677019</v>
       </c>
       <c r="R13" t="n">
-        <v>7111130</v>
+        <v>7110882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,11 +1852,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1883,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103618175</v>
+        <v>103618177</v>
       </c>
       <c r="B14" t="n">
-        <v>92539</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,21 +1879,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1918,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677007</v>
+        <v>676895</v>
       </c>
       <c r="R14" t="n">
-        <v>7111327</v>
+        <v>7111193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,11 +1949,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1985,32 +1965,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103618202</v>
+        <v>103618178</v>
       </c>
       <c r="B15" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2000,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677033</v>
+        <v>676894</v>
       </c>
       <c r="R15" t="n">
-        <v>7110867</v>
+        <v>7111152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,11 +2046,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>kolad stubbe</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2087,14 +2062,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103618194</v>
+        <v>103618181</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2122,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676989</v>
+        <v>676930</v>
       </c>
       <c r="R16" t="n">
-        <v>7111008</v>
+        <v>7111133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,32 +2159,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103618173</v>
+        <v>103618186</v>
       </c>
       <c r="B17" t="n">
-        <v>90283</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>677052</v>
+        <v>676959</v>
       </c>
       <c r="R17" t="n">
-        <v>7111378</v>
+        <v>7111121</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,11 +2240,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2286,14 +2256,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103618190</v>
+        <v>103618187</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2321,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676990</v>
+        <v>676978</v>
       </c>
       <c r="R18" t="n">
-        <v>7111030</v>
+        <v>7111086</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,14 +2353,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103618178</v>
+        <v>103618188</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2418,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676894</v>
+        <v>676971</v>
       </c>
       <c r="R19" t="n">
-        <v>7111152</v>
+        <v>7111054</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,48 +2450,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107162697</v>
+        <v>103618189</v>
       </c>
       <c r="B20" t="n">
-        <v>56476</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100077</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storaggan (AC601), Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676364</v>
+        <v>676976</v>
       </c>
       <c r="R20" t="n">
-        <v>7111147</v>
+        <v>7111034</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2543,19 +2513,14 @@
           <t>Fredrika</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>AC601</t>
-        </is>
-      </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2016-09-06</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2016-09-06</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2570,64 +2535,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Darius Strasevicius</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Darius Strasevicius</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Utter barmarksinventering RMÖ/GDP</t>
-        </is>
-      </c>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1990837</v>
+        <v>103618190</v>
       </c>
       <c r="B21" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>11 km ONO om Fredrika, Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676461</v>
+        <v>676990</v>
       </c>
       <c r="R21" t="n">
-        <v>7111499</v>
+        <v>7111030</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2651,12 +2612,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2005-07-31</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2005-07-31</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2671,26 +2632,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103618188</v>
+        <v>103618194</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2718,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676971</v>
+        <v>676989</v>
       </c>
       <c r="R22" t="n">
-        <v>7111054</v>
+        <v>7111008</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,32 +2741,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103618193</v>
+        <v>103618195</v>
       </c>
       <c r="B23" t="n">
-        <v>91210</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2815,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676979</v>
+        <v>676992</v>
       </c>
       <c r="R23" t="n">
-        <v>7111017</v>
+        <v>7110988</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2861,11 +2822,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2882,14 +2838,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103618186</v>
+        <v>103618196</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2917,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676959</v>
+        <v>676996</v>
       </c>
       <c r="R24" t="n">
-        <v>7111121</v>
+        <v>7110957</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,45 +2935,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>84766646</v>
+        <v>103618199</v>
       </c>
       <c r="B25" t="n">
-        <v>79987</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Yttersjön, Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676015</v>
+        <v>677009</v>
       </c>
       <c r="R25" t="n">
-        <v>7111072</v>
+        <v>7110884</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3044,12 +3000,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3064,22 +3020,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103618159</v>
+        <v>103618202</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3087,21 +3043,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3111,10 +3067,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>677167</v>
+        <v>677033</v>
       </c>
       <c r="R26" t="n">
-        <v>7111508</v>
+        <v>7110867</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3157,6 +3113,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3173,10 +3134,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103618167</v>
+        <v>103618183</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3184,21 +3145,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3208,10 +3169,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677077</v>
+        <v>676935</v>
       </c>
       <c r="R27" t="n">
-        <v>7111446</v>
+        <v>7111134</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3254,6 +3215,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3270,32 +3236,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103618017</v>
+        <v>103618182</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>80468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3305,10 +3271,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>677101</v>
+        <v>676935</v>
       </c>
       <c r="R28" t="n">
-        <v>7110870</v>
+        <v>7111134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3351,6 +3317,11 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3367,10 +3338,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103618203</v>
+        <v>60175868</v>
       </c>
       <c r="B29" t="n">
-        <v>92551</v>
+        <v>29424</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3378,37 +3349,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>103271</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tajgahumla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bombus cingulatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Wahlberg, 1855</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+          <t>Lögdeälven rasbrant vid Bäverhydda, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677034</v>
+        <v>676894</v>
       </c>
       <c r="R29" t="n">
-        <v>7110861</v>
+        <v>7110878</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3432,12 +3412,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3452,44 +3432,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Carl Jansson</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103618170</v>
+        <v>103618204</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>97989</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3499,10 +3479,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>677071</v>
+        <v>677001</v>
       </c>
       <c r="R30" t="n">
-        <v>7111398</v>
+        <v>7110802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3561,10 +3541,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103618189</v>
+        <v>103618173</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>90932</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3572,21 +3552,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3596,10 +3576,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676976</v>
+        <v>677052</v>
       </c>
       <c r="R31" t="n">
-        <v>7111034</v>
+        <v>7111378</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3642,6 +3622,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3658,10 +3643,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103618201</v>
+        <v>103618174</v>
       </c>
       <c r="B32" t="n">
-        <v>78647</v>
+        <v>90932</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3669,21 +3654,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3693,10 +3678,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>677035</v>
+        <v>677004</v>
       </c>
       <c r="R32" t="n">
-        <v>7110865</v>
+        <v>7111334</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3760,50 +3745,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103618016</v>
+        <v>103618175</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>93201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>677102</v>
+        <v>677007</v>
       </c>
       <c r="R33" t="n">
-        <v>7110869</v>
+        <v>7111327</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,11 +3818,6 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3854,7 +3829,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -3872,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112605592</v>
+        <v>112605591</v>
       </c>
       <c r="B34" t="n">
-        <v>92571</v>
+        <v>93209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3883,21 +3858,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3907,10 +3882,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676909</v>
+        <v>676654</v>
       </c>
       <c r="R34" t="n">
-        <v>7111461</v>
+        <v>7111614</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,45 +3949,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103618200</v>
+        <v>112605592</v>
       </c>
       <c r="B35" t="n">
-        <v>90001</v>
+        <v>93235</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+          <t>Fredrika, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>677019</v>
+        <v>676909</v>
       </c>
       <c r="R35" t="n">
-        <v>7110882</v>
+        <v>7111461</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4039,12 +4014,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2022-10-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4059,26 +4039,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103618166</v>
+        <v>103618167</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4106,10 +4086,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>677091</v>
+        <v>677077</v>
       </c>
       <c r="R36" t="n">
-        <v>7111471</v>
+        <v>7111446</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,14 +4148,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103618177</v>
+        <v>103618169</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4203,10 +4183,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>676895</v>
+        <v>677073</v>
       </c>
       <c r="R37" t="n">
-        <v>7111193</v>
+        <v>7111423</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4265,32 +4245,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>103618183</v>
+        <v>103618170</v>
       </c>
       <c r="B38" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4300,10 +4280,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676935</v>
+        <v>677071</v>
       </c>
       <c r="R38" t="n">
-        <v>7111134</v>
+        <v>7111398</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4346,11 +4326,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4367,32 +4342,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>103618020</v>
+        <v>103618176</v>
       </c>
       <c r="B39" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4402,10 +4377,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>677175</v>
+        <v>676934</v>
       </c>
       <c r="R39" t="n">
-        <v>7110865</v>
+        <v>7111243</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4464,10 +4439,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>103618176</v>
+        <v>103618172</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4475,21 +4450,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4499,10 +4474,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>676934</v>
+        <v>677055</v>
       </c>
       <c r="R40" t="n">
-        <v>7111243</v>
+        <v>7111386</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4545,6 +4520,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4561,10 +4541,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>103618199</v>
+        <v>112605593</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4572,34 +4552,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+          <t>Fredrika, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>677009</v>
+        <v>676808</v>
       </c>
       <c r="R41" t="n">
-        <v>7110884</v>
+        <v>7111580</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4626,12 +4606,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2022-10-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4646,22 +4631,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>103618169</v>
+        <v>119796272</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4669,34 +4654,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+          <t>Fredrika, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>677073</v>
+        <v>676855</v>
       </c>
       <c r="R42" t="n">
-        <v>7111423</v>
+        <v>7111501</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,12 +4712,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4743,44 +4737,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>103618158</v>
+        <v>103618020</v>
       </c>
       <c r="B43" t="n">
-        <v>98382</v>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4790,10 +4784,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>677168</v>
+        <v>677175</v>
       </c>
       <c r="R43" t="n">
-        <v>7111509</v>
+        <v>7110865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4852,14 +4846,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>103618197</v>
+        <v>103618042</v>
       </c>
       <c r="B44" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4887,10 +4881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>676997</v>
+        <v>677402</v>
       </c>
       <c r="R44" t="n">
-        <v>7110951</v>
+        <v>7111133</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4949,10 +4943,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>60175892</v>
+        <v>103618043</v>
       </c>
       <c r="B45" t="n">
-        <v>19902</v>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4960,50 +4954,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102001</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Urskogsvedfluga</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Xylophagus kowarzi</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pleske, 1925)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lögdeälven rasbrant vid Bäverhydda, Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>676894</v>
+        <v>677411</v>
       </c>
       <c r="R45" t="n">
-        <v>7110878</v>
+        <v>7111164</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5027,17 +5008,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Sydlänt rasbrant med stora mängder död ved av asp och björk.</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5052,76 +5028,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15371640</v>
+        <v>103618017</v>
       </c>
       <c r="B46" t="n">
-        <v>30266</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100840</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallvägstekel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Deuteragenia vechti</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Day, 1979)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Käringberget, Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>676708</v>
+        <v>677101</v>
       </c>
       <c r="R46" t="n">
-        <v>7111467</v>
+        <v>7110870</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5148,27 +5105,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2012-06-01</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2012-08-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sveaskog 19</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5183,26 +5125,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103618160</v>
+        <v>103618035</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5230,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>677135</v>
+        <v>677355</v>
       </c>
       <c r="R47" t="n">
-        <v>7111507</v>
+        <v>7111027</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5292,14 +5234,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103618187</v>
+        <v>103618037</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5327,10 +5269,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>676978</v>
+        <v>677361</v>
       </c>
       <c r="R48" t="n">
-        <v>7111086</v>
+        <v>7111059</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5389,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103618198</v>
+        <v>103618040</v>
       </c>
       <c r="B49" t="n">
-        <v>90283</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5424,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>677013</v>
+        <v>677400</v>
       </c>
       <c r="R49" t="n">
-        <v>7110889</v>
+        <v>7111126</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5470,11 +5412,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5491,32 +5428,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103618164</v>
+        <v>103618033</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>80468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5526,10 +5463,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>677114</v>
+        <v>677344</v>
       </c>
       <c r="R50" t="n">
-        <v>7111487</v>
+        <v>7111031</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5572,6 +5509,11 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5588,38 +5530,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103618022</v>
+        <v>103618016</v>
       </c>
       <c r="B51" t="n">
-        <v>8436</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5628,10 +5570,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>677240</v>
+        <v>677102</v>
       </c>
       <c r="R51" t="n">
-        <v>7110881</v>
+        <v>7110869</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5666,6 +5608,11 @@
           <t>2022-09-17</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5677,7 +5624,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>död björl</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5695,10 +5642,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112605591</v>
+        <v>103618032</v>
       </c>
       <c r="B52" t="n">
-        <v>92547</v>
+        <v>4872</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5706,34 +5653,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4366</v>
+        <v>101675</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fredrika, Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>676654</v>
+        <v>677339</v>
       </c>
       <c r="R52" t="n">
-        <v>7111614</v>
+        <v>7111023</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5760,17 +5712,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5781,61 +5728,71 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>asplåga</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112605593</v>
+        <v>103618022</v>
       </c>
       <c r="B53" t="n">
-        <v>80083</v>
+        <v>8444</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fredrika, Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>676808</v>
+        <v>677240</v>
       </c>
       <c r="R53" t="n">
-        <v>7111580</v>
+        <v>7110881</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5862,17 +5819,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5883,64 +5835,69 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>död björl</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>65116413</v>
+        <v>103618047</v>
       </c>
       <c r="B54" t="n">
-        <v>38945</v>
+        <v>92692</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>255941</v>
+        <v>1958</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tromatobia forsiusi</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hellén, 1915)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>malaisefälla</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögdeälven vid Käringberget, Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>676893</v>
+        <v>677472</v>
       </c>
       <c r="R54" t="n">
-        <v>7110878</v>
+        <v>7111260</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5964,17 +5921,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>För exakt fynddatum kontakta rapportör</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5989,57 +5941,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>84766650</v>
+        <v>103618045</v>
       </c>
       <c r="B55" t="n">
-        <v>80083</v>
+        <v>93213</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Yttersjön, Ås lm</t>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>675874</v>
+        <v>677450</v>
       </c>
       <c r="R55" t="n">
-        <v>7111403</v>
+        <v>7111210</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6066,12 +6018,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6086,26 +6038,26 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Aron Dynesius</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103618181</v>
+        <v>103618046</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6133,10 +6085,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>676930</v>
+        <v>677464</v>
       </c>
       <c r="R56" t="n">
-        <v>7111133</v>
+        <v>7111238</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6192,6 +6144,787 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>103618156</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>677185</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7111513</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>103618159</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>677167</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7111508</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>103618160</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>677135</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7111507</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>103618164</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>677114</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7111487</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>103618166</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>677091</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7111471</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>103618157</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>677176</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7111509</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>103618161</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>677129</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7111504</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>103618158</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Käringbergets S-sluttningar, Käringbergets EP, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>677168</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7111509</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
